--- a/demo-assets/coolair_sales_week38.xlsx
+++ b/demo-assets/coolair_sales_week38.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="113">
   <si>
     <t>Serial number</t>
   </si>
@@ -43,193 +43,196 @@
     <t>AER-SPL15</t>
   </si>
   <si>
+    <t>R. Kulkarni</t>
+  </si>
+  <si>
+    <t>+91 90000 00101</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>CA-INV-38001</t>
+  </si>
+  <si>
+    <t>AER-SPL15-260902</t>
+  </si>
+  <si>
+    <t>B. Kadam</t>
+  </si>
+  <si>
+    <t>+91 90000 00202</t>
+  </si>
+  <si>
+    <t>CA-INV-38002</t>
+  </si>
+  <si>
+    <t>AER-SPL15-260903</t>
+  </si>
+  <si>
+    <t>C. Thakur</t>
+  </si>
+  <si>
+    <t>+91 90000 00203</t>
+  </si>
+  <si>
+    <t>customer3@example.com</t>
+  </si>
+  <si>
+    <t>CA-INV-38003</t>
+  </si>
+  <si>
+    <t>AER-SPL18-260904</t>
+  </si>
+  <si>
+    <t>AER-SPL18</t>
+  </si>
+  <si>
+    <t>D. Deshmukh</t>
+  </si>
+  <si>
+    <t>+91 90000 00204</t>
+  </si>
+  <si>
+    <t>Pimpri</t>
+  </si>
+  <si>
+    <t>CA-INV-38004</t>
+  </si>
+  <si>
+    <t>AER-SPL15-260905</t>
+  </si>
+  <si>
+    <t>G. Naik</t>
+  </si>
+  <si>
+    <t>+91 90000 00205</t>
+  </si>
+  <si>
+    <t>Hinjewadi</t>
+  </si>
+  <si>
+    <t>CA-INV-38005</t>
+  </si>
+  <si>
+    <t>AER-SPL15-260906</t>
+  </si>
+  <si>
+    <t>J. Yadav</t>
+  </si>
+  <si>
+    <t>+91 90000 00206</t>
+  </si>
+  <si>
+    <t>customer6@example.com</t>
+  </si>
+  <si>
+    <t>Kharadi</t>
+  </si>
+  <si>
+    <t>CA-INV-38006</t>
+  </si>
+  <si>
+    <t>AER-SPL15-260907</t>
+  </si>
+  <si>
+    <t>AER-SPL20</t>
+  </si>
+  <si>
+    <t>K. Jadhav</t>
+  </si>
+  <si>
+    <t>+91 90000 00207</t>
+  </si>
+  <si>
+    <t>CA-INV-38007</t>
+  </si>
+  <si>
+    <t>AER-SPL18-260908</t>
+  </si>
+  <si>
+    <t>L. Shinde</t>
+  </si>
+  <si>
+    <t>+91 90000 00208</t>
+  </si>
+  <si>
+    <t>CA-INV-38008</t>
+  </si>
+  <si>
+    <t>AER-SPL15-260909</t>
+  </si>
+  <si>
+    <t>M. Chavan</t>
+  </si>
+  <si>
+    <t>+91 90000 00209</t>
+  </si>
+  <si>
+    <t>customer9@example.com</t>
+  </si>
+  <si>
+    <t>CA-INV-38009</t>
+  </si>
+  <si>
+    <t>AER-SPL15-260910</t>
+  </si>
+  <si>
+    <t>N. Mane</t>
+  </si>
+  <si>
+    <t>+91 90000 00210</t>
+  </si>
+  <si>
+    <t>CA-INV-38010</t>
+  </si>
+  <si>
+    <t>AER-SPL15-260911</t>
+  </si>
+  <si>
+    <t>P. Wagh</t>
+  </si>
+  <si>
+    <t>+91 90000 00211</t>
+  </si>
+  <si>
+    <t>CA-INV-38011</t>
+  </si>
+  <si>
+    <t>AER-SPL18-260912</t>
+  </si>
+  <si>
+    <t>R. Gaikwad</t>
+  </si>
+  <si>
+    <t>+91 90000 00212</t>
+  </si>
+  <si>
+    <t>customer12@example.com</t>
+  </si>
+  <si>
+    <t>CA-INV-38012</t>
+  </si>
+  <si>
+    <t>AER-SPL15-260913</t>
+  </si>
+  <si>
+    <t>S. Sawant</t>
+  </si>
+  <si>
+    <t>+91 90000 00213</t>
+  </si>
+  <si>
+    <t>CA-INV-38013</t>
+  </si>
+  <si>
+    <t>AER-SPL15-260914</t>
+  </si>
+  <si>
     <t>A. Bhosale</t>
-  </si>
-  <si>
-    <t>+91 90000 00201</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Pune</t>
-  </si>
-  <si>
-    <t>CA-INV-38001</t>
-  </si>
-  <si>
-    <t>AER-SPL15-260902</t>
-  </si>
-  <si>
-    <t>B. Kadam</t>
-  </si>
-  <si>
-    <t>+91 90000 00202</t>
-  </si>
-  <si>
-    <t>CA-INV-38002</t>
-  </si>
-  <si>
-    <t>AER-SPL15-260903</t>
-  </si>
-  <si>
-    <t>C. Thakur</t>
-  </si>
-  <si>
-    <t>+91 90000 00203</t>
-  </si>
-  <si>
-    <t>customer3@example.com</t>
-  </si>
-  <si>
-    <t>CA-INV-38003</t>
-  </si>
-  <si>
-    <t>AER-SPL18-260904</t>
-  </si>
-  <si>
-    <t>AER-SPL18</t>
-  </si>
-  <si>
-    <t>D. Deshmukh</t>
-  </si>
-  <si>
-    <t>+91 90000 00204</t>
-  </si>
-  <si>
-    <t>Pimpri</t>
-  </si>
-  <si>
-    <t>CA-INV-38004</t>
-  </si>
-  <si>
-    <t>AER-SPL15-260905</t>
-  </si>
-  <si>
-    <t>G. Naik</t>
-  </si>
-  <si>
-    <t>+91 90000 00205</t>
-  </si>
-  <si>
-    <t>Hinjewadi</t>
-  </si>
-  <si>
-    <t>CA-INV-38005</t>
-  </si>
-  <si>
-    <t>AER-SPL15-260906</t>
-  </si>
-  <si>
-    <t>J. Yadav</t>
-  </si>
-  <si>
-    <t>+91 90000 00206</t>
-  </si>
-  <si>
-    <t>customer6@example.com</t>
-  </si>
-  <si>
-    <t>Kharadi</t>
-  </si>
-  <si>
-    <t>CA-INV-38006</t>
-  </si>
-  <si>
-    <t>AER-SPL15-260907</t>
-  </si>
-  <si>
-    <t>AER-SPL20</t>
-  </si>
-  <si>
-    <t>K. Jadhav</t>
-  </si>
-  <si>
-    <t>+91 90000 00207</t>
-  </si>
-  <si>
-    <t>CA-INV-38007</t>
-  </si>
-  <si>
-    <t>AER-SPL18-260908</t>
-  </si>
-  <si>
-    <t>L. Shinde</t>
-  </si>
-  <si>
-    <t>+91 90000 00208</t>
-  </si>
-  <si>
-    <t>CA-INV-38008</t>
-  </si>
-  <si>
-    <t>AER-SPL15-260909</t>
-  </si>
-  <si>
-    <t>M. Chavan</t>
-  </si>
-  <si>
-    <t>+91 90000 00209</t>
-  </si>
-  <si>
-    <t>customer9@example.com</t>
-  </si>
-  <si>
-    <t>CA-INV-38009</t>
-  </si>
-  <si>
-    <t>AER-SPL15-260910</t>
-  </si>
-  <si>
-    <t>N. Mane</t>
-  </si>
-  <si>
-    <t>+91 90000 00210</t>
-  </si>
-  <si>
-    <t>CA-INV-38010</t>
-  </si>
-  <si>
-    <t>AER-SPL15-260911</t>
-  </si>
-  <si>
-    <t>P. Wagh</t>
-  </si>
-  <si>
-    <t>+91 90000 00211</t>
-  </si>
-  <si>
-    <t>CA-INV-38011</t>
-  </si>
-  <si>
-    <t>AER-SPL18-260912</t>
-  </si>
-  <si>
-    <t>R. Gaikwad</t>
-  </si>
-  <si>
-    <t>+91 90000 00212</t>
-  </si>
-  <si>
-    <t>customer12@example.com</t>
-  </si>
-  <si>
-    <t>CA-INV-38012</t>
-  </si>
-  <si>
-    <t>AER-SPL15-260913</t>
-  </si>
-  <si>
-    <t>S. Sawant</t>
-  </si>
-  <si>
-    <t>+91 90000 00213</t>
-  </si>
-  <si>
-    <t>CA-INV-38013</t>
-  </si>
-  <si>
-    <t>AER-SPL15-260914</t>
   </si>
   <si>
     <t>+91 90000 00214</t>
@@ -1114,10 +1117,10 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -1129,12 +1132,12 @@
         <v>46280</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -1143,10 +1146,10 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
@@ -1155,12 +1158,12 @@
         <v>46281</v>
       </c>
       <c r="H16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
@@ -1169,7 +1172,7 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -1181,12 +1184,12 @@
         <v>46282</v>
       </c>
       <c r="H17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -1195,7 +1198,7 @@
         <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -1207,12 +1210,12 @@
         <v>46283</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
@@ -1221,10 +1224,10 @@
         <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s">
         <v>39</v>
@@ -1233,12 +1236,12 @@
         <v>46284</v>
       </c>
       <c r="H19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -1247,7 +1250,7 @@
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -1259,12 +1262,12 @@
         <v>46279</v>
       </c>
       <c r="H20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
@@ -1273,7 +1276,7 @@
         <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
@@ -1285,12 +1288,12 @@
         <v>46280</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
@@ -1299,10 +1302,10 @@
         <v>47</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -1311,12 +1314,12 @@
         <v>46281</v>
       </c>
       <c r="H22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
@@ -1325,7 +1328,7 @@
         <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -1335,12 +1338,12 @@
       </c>
       <c r="G23" s="1"/>
       <c r="H23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
@@ -1349,7 +1352,7 @@
         <v>56</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
@@ -1361,12 +1364,12 @@
         <v>46283</v>
       </c>
       <c r="H24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" t="s">
         <v>25</v>
@@ -1375,10 +1378,10 @@
         <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s">
         <v>39</v>
@@ -1387,12 +1390,12 @@
         <v>46284</v>
       </c>
       <c r="H25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
@@ -1401,7 +1404,7 @@
         <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E26" t="s">
         <v>12</v>
@@ -1413,7 +1416,7 @@
         <v>46279</v>
       </c>
       <c r="H26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
